--- a/data/gravel/Primos Super Dame 2025.xlsx
+++ b/data/gravel/Primos Super Dame 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F591A-6CD3-9F4B-A341-EC6744253E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CC8BFB-4437-D342-87EB-668914C906DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="1060" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6700" yWindow="500" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -436,6 +436,9 @@
   </si>
   <si>
     <t>a8:f35</t>
+  </si>
+  <si>
+    <t>https://primoscycles.com/cdn/shop/files/SuperDame_2025_GreyAsh_01_4ab2d543-a30d-4e8e-ac03-60378862bafe.png?v=1757978850&amp;width=1620</t>
   </si>
 </sst>
 </file>
@@ -842,6 +845,11 @@
         <v>114</v>
       </c>
     </row>
+    <row r="6" spans="1:10">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Primos Super Dame 2025.xlsx
+++ b/data/gravel/Primos Super Dame 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CC8BFB-4437-D342-87EB-668914C906DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338F800A-FAB0-CE46-AF58-D618D9EEA240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6700" yWindow="500" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -439,6 +439,12 @@
   </si>
   <si>
     <t>https://primoscycles.com/cdn/shop/files/SuperDame_2025_GreyAsh_01_4ab2d543-a30d-4e8e-ac03-60378862bafe.png?v=1757978850&amp;width=1620</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Portland, Oregon, USA</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1656,6 +1662,14 @@
         <v>96</v>
       </c>
     </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Primos Super Dame 2025.xlsx
+++ b/data/gravel/Primos Super Dame 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338F800A-FAB0-CE46-AF58-D618D9EEA240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BF919F-3CA5-2841-891C-154F953457B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="500" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31000" yWindow="-23100" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1347,22 +1347,10 @@
       <c r="A34" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="4">
-        <f>C36*2.54</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="4">
-        <f t="shared" ref="D34:F35" si="0">D36*2.54</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
       <c r="H34" s="5" t="s">
         <v>99</v>
       </c>
@@ -1371,22 +1359,10 @@
       <c r="A35" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="4">
-        <f>C37*2.54</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
       <c r="H35" s="5" t="s">
         <v>100</v>
       </c>

--- a/data/gravel/Primos Super Dame 2025.xlsx
+++ b/data/gravel/Primos Super Dame 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BF919F-3CA5-2841-891C-154F953457B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05A3B84-67B5-5744-A33D-345ED5F59F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31000" yWindow="-23100" windowWidth="22100" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -445,6 +445,24 @@
   </si>
   <si>
     <t>Portland, Oregon, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -805,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1488,161 +1506,191 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54">
-        <v>27.2</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>122</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B60">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>97</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73">
-        <v>1499</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
         <v>117</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>118</v>
       </c>
     </row>
